--- a/Business plan/Готовые документы/VitaGen_Финансовая_модель.xlsx
+++ b/Business plan/Готовые документы/VitaGen_Финансовая_модель.xlsx
@@ -218,7 +218,7 @@
     <t>~20–25%</t>
   </si>
   <si>
-    <t>Экспертная оценка: концентрация федеральных центров ВРТ и НМИЦ; ~25–30 тыс. циклов/год</t>
+    <t>Экспертная оценка: концентрация федеральных центров ВРТ и РНИМУ; ~25–30 тыс. циклов/год</t>
   </si>
   <si>
     <t>Средняя стоимость коммерческого цикла (Москва)</t>
@@ -227,7 +227,7 @@
     <t>250–450 тыс. ₽</t>
   </si>
   <si>
-    <t>Открытые прайсы клиник (НМИЦ, коммерческие центры), 2024–2025 гг.</t>
+    <t>Открытые прайсы клиник (РНИМУ, коммерческие центры), 2024–2025 гг.</t>
   </si>
   <si>
     <t>Средняя стоимость цикла по ОМС (тариф)</t>
